--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_po_receipts_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_po_receipts_2024.xlsx
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALPO-9000000003</t>
+          <t>PO 9001000003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALPO-9000000005</t>
+          <t>PO 9001000005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALPO-9000000008</t>
+          <t>PO 9001000008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALPO-9000000010</t>
+          <t>PO 9001000010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
